--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -36076,6 +36076,7 @@
       <c r="AB1030" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N155"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>